--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370869</v>
       </c>
       <c r="B3" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370879</v>
       </c>
       <c r="B4" t="n">
-        <v>78875</v>
+        <v>78880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370878</v>
       </c>
       <c r="B5" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137370870</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137370880</v>
       </c>
       <c r="B12" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137370875</v>
       </c>
       <c r="B13" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137370872</v>
       </c>
       <c r="B14" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137370877</v>
       </c>
       <c r="B15" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370869</v>
       </c>
       <c r="B3" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370879</v>
       </c>
       <c r="B4" t="n">
-        <v>78880</v>
+        <v>78891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370878</v>
       </c>
       <c r="B5" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137370870</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137370880</v>
       </c>
       <c r="B12" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137370875</v>
       </c>
       <c r="B13" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137370877</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370869</v>
       </c>
       <c r="B3" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370879</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>78892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370878</v>
       </c>
       <c r="B5" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137370870</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137370880</v>
       </c>
       <c r="B12" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137370875</v>
       </c>
       <c r="B13" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137370877</v>
       </c>
       <c r="B15" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370869</v>
       </c>
       <c r="B3" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370879</v>
       </c>
       <c r="B4" t="n">
-        <v>78892</v>
+        <v>78894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370878</v>
       </c>
       <c r="B5" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137370870</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137370880</v>
       </c>
       <c r="B12" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137370875</v>
       </c>
       <c r="B13" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137370877</v>
       </c>
       <c r="B15" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35203-2025 artfynd.xlsx
+++ b/artfynd/A 35203-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370884</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370869</v>
       </c>
       <c r="B3" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370879</v>
       </c>
       <c r="B4" t="n">
-        <v>78894</v>
+        <v>78898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370878</v>
       </c>
       <c r="B5" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370876</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370883</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137370881</v>
       </c>
       <c r="B8" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137370882</v>
       </c>
       <c r="B9" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137370871</v>
       </c>
       <c r="B10" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137370870</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137370880</v>
       </c>
       <c r="B12" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137370875</v>
       </c>
       <c r="B13" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137370872</v>
       </c>
       <c r="B14" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137370877</v>
       </c>
       <c r="B15" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
